--- a/square_ready/BASELINE_CURRENT/BASELINE_CATEGORY_PLAN.xlsx
+++ b/square_ready/BASELINE_CURRENT/BASELINE_CATEGORY_PLAN.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,17 +451,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AZCS</t>
+          <t>AZ Cleaning Supplies</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AZCS &gt; Chemicals</t>
+          <t>AZ Cleaning Supplies &gt; Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AZCS &gt; Chemicals</t>
+          <t>AZ Cleaning Supplies &gt; Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,44 +471,44 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sodium Hydroxide - 50 lb Bag</t>
+          <t>Repair / Service Labor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sodium Hydroxide - 50 lb Bag</t>
+          <t>Repair / Service Labor</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>AZCS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BE &gt; Cold Water Equipment</t>
+          <t>AZCS &gt; Chemicals</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BE &gt; Cold Water Equipment</t>
+          <t>AZCS &gt; Chemicals</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CW, 2-STEP, ELEC, 4GPM, 2000PSI, 5HP, 3PH 208VAC@17A/230VAC@16A</t>
+          <t>Sodium Hydroxide - 50 lb Bag</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CW; 2-STEP, ELECTRIC, 5GPM@2000PSI, 7.5HP, 1PH 230VAC@36A</t>
+          <t>Sodium Hydroxide - 50 lb Bag</t>
         </is>
       </c>
     </row>
@@ -520,27 +520,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment</t>
+          <t>BE &gt; Cold Water Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 001-200</t>
+          <t>BE &gt; Cold Water Equipment</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>"T" TYPE SCREW FOR 3" TP KIT OF 6</t>
+          <t>CW, 2-STEP, ELEC, 4GPM, 2000PSI, 5HP, 3PH 208VAC@17A/230VAC@16A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BLADE ASSY, 30" FOR JINLING FP30. NLA</t>
+          <t>CW; 2-STEP, ELECTRIC, 5GPM@2000PSI, 7.5HP, 1PH 230VAC@36A</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 201-400</t>
+          <t>BE &gt; Equipment &gt; 001-200</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -567,12 +567,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BLADE ASSY, 36" FOR JINLING FD36. NLA</t>
+          <t>"T" TYPE SCREW FOR 3" TP KIT OF 6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CAMLOCKFITTING,PP3"TYPE DP</t>
+          <t>BLADE ASSY, 30" FOR JINLING FP30. NLA</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 401-600</t>
+          <t>BE &gt; Equipment &gt; 201-400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CAP SCREW, LOW PRESSURE FOR EZ4040G</t>
+          <t>BLADE ASSY, 36" FOR JINLING FD36. NLA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DECAL, CASE N0ZZLE PLATE FOR 85.600.210C FRAME. NLA</t>
+          <t>CAMLOCKFITTING,PP3"TYPE DP</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 601-800</t>
+          <t>BE &gt; Equipment &gt; 401-600</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DECAL, CONTACT, PW FOR 2705HWX/3170RWX/3065HWX/2560RW</t>
+          <t>CAP SCREW, LOW PRESSURE FOR EZ4040G</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FRAME, LARGE, BE, GREY STEEL TIP BACK W/O WHEELS</t>
+          <t>DECAL, CASE N0ZZLE PLATE FOR 85.600.210C FRAME. NLA</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 801-1000</t>
+          <t>BE &gt; Equipment &gt; 601-800</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -663,12 +663,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FRAME, LARGE, BE, STAINLESS STEEL TIP BACK W/O WHEELS</t>
+          <t>DECAL, CONTACT, PW FOR 2705HWX/3170RWX/3065HWX/2560RW</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>HOSE 40" 3/8" S/B BLK BARE 4000 PSI</t>
+          <t>FRAME, LARGE, BE, GREY STEEL TIP BACK W/O WHEELS</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 1001-1200</t>
+          <t>BE &gt; Equipment &gt; 801-1000</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -695,12 +695,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HOSE 50FT 3/8" D/B BLK SS QC 6000 PSI.</t>
+          <t>FRAME, LARGE, BE, STAINLESS STEEL TIP BACK W/O WHEELS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KIT, COM BXD PUMP REBUILD FOR 85.149.081 / 088 PUMP</t>
+          <t>HOSE 40" 3/8" S/B BLK BARE 4000 PSI</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 1201-1400</t>
+          <t>BE &gt; Equipment &gt; 1001-1200</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KIT, COMPLETE COUPLER/PLUG w/85.300.101,102,103 &amp; 104. RB: 85.400.207</t>
+          <t>HOSE 50FT 3/8" D/B BLK SS QC 6000 PSI.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NOZZLE, FUEL; 90A, 2.0GPH BRASS. FOR HW4013HG</t>
+          <t>KIT, COM BXD PUMP REBUILD FOR 85.149.081 / 088 PUMP</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 1401-1600</t>
+          <t>BE &gt; Equipment &gt; 1201-1400</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NOZZLE, LONG RANGE SOAP LONG &amp; SHORT RANGE ADJ NOZZLE</t>
+          <t>KIT, COMPLETE COUPLER/PLUG w/85.300.101,102,103 &amp; 104. RB: 85.400.207</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>O'RING, FOR COMET PUMP FOR COMET PUMP</t>
+          <t>NOZZLE, FUEL; 90A, 2.0GPH BRASS. FOR HW4013HG</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 1601-1800</t>
+          <t>BE &gt; Equipment &gt; 1401-1600</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>O'RING, FOR PISTON (LWDK) NOT RETURNABLE TO SUPPLIER</t>
+          <t>NOZZLE, LONG RANGE SOAP LONG &amp; SHORT RANGE ADJ NOZZLE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PUMP BODY; 85.150.315 2HP50 PUMP, WS1565H</t>
+          <t>O'RING, FOR COMET PUMP FOR COMET PUMP</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 1801-2000</t>
+          <t>BE &gt; Equipment &gt; 1601-1800</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PUMP BOXED RMV25G30D-EZ 3K 2.5 GPM HORIZ - BRASS HEAD</t>
+          <t>O'RING, FOR PISTON (LWDK) NOT RETURNABLE TO SUPPLIER</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEAL, OIL (EZ3040G)</t>
+          <t>PUMP BODY; 85.150.315 2HP50 PUMP, WS1565H</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 2001-2200</t>
+          <t>BE &gt; Equipment &gt; 1801-2000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -855,12 +855,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SEAL, OIL FOR CAT 2X, 1DX, 2DX, 3DX, 4DX PUMPS</t>
+          <t>PUMP BOXED RMV25G30D-EZ 3K 2.5 GPM HORIZ - BRASS HEAD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UNLOADER PILOT VALVE 160PSI LOAD; 175PSI UNLOAD</t>
+          <t>SEAL, OIL (EZ3040G)</t>
         </is>
       </c>
     </row>
@@ -877,22 +877,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BE &gt; Equipment &gt; 2201-2357</t>
+          <t>BE &gt; Equipment &gt; 2001-2200</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNLOADER VALVE FOR AR JRV PUMP</t>
+          <t>SEAL, OIL FOR CAT 2X, 1DX, 2DX, 3DX, 4DX PUMPS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WHORL CASE, WP, 4", OLD FOR 85.150.204. WQL/NLA</t>
+          <t>UNLOADER PILOT VALVE 160PSI LOAD; 175PSI UNLOAD</t>
         </is>
       </c>
     </row>
@@ -904,27 +904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BE &gt; Hot Water Equipment</t>
+          <t>BE &gt; Equipment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BE &gt; Hot Water Equipment</t>
+          <t>BE &gt; Equipment &gt; 2201-2357</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>157</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HW, 240V, 2500PSI 3.5GPM 5HP, ABB, COMET, 1PH, NAT GAS</t>
+          <t>UNLOADER VALVE FOR AR JRV PUMP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HW, STN, HD, 7.5HP, 4GPM@3000PSI, 3PH NG, COIL R/L, 460VAC@16A, 1.5" FRAME</t>
+          <t>WHORL CASE, WP, 4", OLD FOR 85.150.204. WQL/NLA</t>
         </is>
       </c>
     </row>
@@ -936,59 +936,59 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BE &gt; Pressure Washers</t>
+          <t>BE &gt; Hot Water Equipment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BE &gt; Pressure Washers</t>
+          <t>BE &gt; Hot Water Equipment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PW ELEC 1.5HP 1500 PSI 1.6 GPM WALLMOUNT W/ HOSE REEL</t>
+          <t>HW, 240V, 2500PSI 3.5GPM 5HP, ABB, COMET, 1PH, NAT GAS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PW; HOT, ELEC, 2000PSI@3.5GPM, 230V AR, 5HP 1PH 230V BELT DRIVE</t>
+          <t>HW, STN, HD, 7.5HP, 4GPM@3000PSI, 3PH NG, COIL R/L, 460VAC@16A, 1.5" FRAME</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Barrens</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Barrens &gt; Accessories &amp; Misc</t>
+          <t>BE &gt; Pressure Washers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Barrens &gt; Accessories &amp; Misc &gt; 001-200</t>
+          <t>BE &gt; Pressure Washers</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>(10)GLADIATOR OVAL MOLDED GRIP 36" CHROME PLATED</t>
+          <t>PW ELEC 1.5HP 1500 PSI 1.6 GPM WALLMOUNT W/ HOSE REEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GP HI-DRAW ADJ ACID INJECT 2.1mm 3-5 GPM</t>
+          <t>PW; HOT, ELEC, 2000PSI@3.5GPM, 230V AR, 5HP 1PH 230V BELT DRIVE</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Barrens &gt; Accessories &amp; Misc &gt; 201-319</t>
+          <t>Barrens &gt; Accessories &amp; Misc &gt; 001-200</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GP REEL MOUNT KIT</t>
+          <t>(10)GLADIATOR OVAL MOLDED GRIP 36" CHROME PLATED</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ZGRS1000 RS500 GEAR REDUCTION 2.2 TO 1 FOR 1" OD S</t>
+          <t>GP HI-DRAW ADJ ACID INJECT 2.1mm 3-5 GPM</t>
         </is>
       </c>
     </row>
@@ -1032,27 +1032,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Barrens &gt; Chemicals &amp; Sealers</t>
+          <t>Barrens &gt; Accessories &amp; Misc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Barrens &gt; Chemicals &amp; Sealers</t>
+          <t>Barrens &gt; Accessories &amp; Misc &gt; 201-319</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43243 LOW PRESSURE SEAL 3FR,7FR</t>
+          <t>GP REEL MOUNT KIT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EACH 16 OZ. RED DEVIL SOOT REMOVER</t>
+          <t>ZGRS1000 RS500 GEAR REDUCTION 2.2 TO 1 FOR 1" OD S</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Barrens &gt; Complete Pumps</t>
+          <t>Barrens &gt; Chemicals &amp; Sealers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Barrens &gt; Complete Pumps &gt; 001-200</t>
+          <t>Barrens &gt; Chemicals &amp; Sealers</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(10)2SFX20ES 2GPM 2000 PSI 3450 RPM 5/8" ELECTRIC</t>
+          <t>43243 LOW PRESSURE SEAL 3FR,7FR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>RK1528HN 4.0GPM 4000PSI 1450RPM 24mm x 30mm SHAFT</t>
+          <t>EACH 16 OZ. RED DEVIL SOOT REMOVER</t>
         </is>
       </c>
     </row>
@@ -1101,22 +1101,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Barrens &gt; Complete Pumps &gt; 201-291</t>
+          <t>Barrens &gt; Complete Pumps &gt; 001-200</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RKA45G40HN 4.5GPM 4000 PSI 1750RPM 24mm SHAFT</t>
+          <t>(10)2SFX20ES 2GPM 2000 PSI 3450 RPM 5/8" ELECTRIC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ZWD5030G 5.0GPM 3000 PSI 1" GAS FLANGE</t>
+          <t>RK1528HN 4.0GPM 4000PSI 1450RPM 24mm x 30mm SHAFT</t>
         </is>
       </c>
     </row>
@@ -1128,27 +1128,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Barrens &gt; Drive Components &amp; Hardware</t>
+          <t>Barrens &gt; Complete Pumps</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Barrens &gt; Drive Components &amp; Hardware</t>
+          <t>Barrens &gt; Complete Pumps &gt; 201-291</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>91</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(10)10 ml BLUE THREADLOCKER</t>
+          <t>RKA45G40HN 4.5GPM 4000 PSI 1750RPM 24mm SHAFT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Y60040951 CHECK SPRING</t>
+          <t>ZWD5030G 5.0GPM 3000 PSI 1" GAS FLANGE</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Barrens &gt; Electrical &amp; Burner Controls</t>
+          <t>Barrens &gt; Drive Components &amp; Hardware</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Barrens &gt; Electrical &amp; Burner Controls</t>
+          <t>Barrens &gt; Drive Components &amp; Hardware</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>177</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(10)PULSAR 4 UNLOADER WITH SWITCH</t>
+          <t>(10)10 ml BLUE THREADLOCKER</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WAYNE MSR-DC 12V BURNER W/7116 PUMP</t>
+          <t>Y60040951 CHECK SPRING</t>
         </is>
       </c>
     </row>
@@ -1192,27 +1192,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Barrens &gt; Engines &amp; Engine Parts</t>
+          <t>Barrens &gt; Electrical &amp; Burner Controls</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Barrens &gt; Engines &amp; Engine Parts</t>
+          <t>Barrens &gt; Electrical &amp; Burner Controls</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>129</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>(12)120-345 STENS OIL FILTERREPLACE BRIGGS 491056</t>
+          <t>(10)PULSAR 4 UNLOADER WITH SWITCH</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZSPEED THROTTLE CONTROL KIT 3000PSI</t>
+          <t>WAYNE MSR-DC 12V BURNER W/7116 PUMP</t>
         </is>
       </c>
     </row>
@@ -1224,27 +1224,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Barrens &gt; Filters &amp; Strainers</t>
+          <t>Barrens &gt; Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Barrens &gt; Filters &amp; Strainers</t>
+          <t>Barrens &gt; Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>157</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(10)CLEAR BOWL WATER FILTER 1" FPT 50 MESH</t>
+          <t>(12)120-345 STENS OIL FILTERREPLACE BRIGGS 491056</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ZF2 CHEMICAL STRAINER W/CHECK VALVE</t>
+          <t>ZSPEED THROTTLE CONTROL KIT 3000PSI</t>
         </is>
       </c>
     </row>
@@ -1256,27 +1256,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Barrens &gt; Fittings &amp; Adapters</t>
+          <t>Barrens &gt; Filters &amp; Strainers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Barrens &gt; Fittings &amp; Adapters &gt; 001-200</t>
+          <t>Barrens &gt; Filters &amp; Strainers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(100)22mm SCREW COUPLER X 22mm SCREW COUPLER</t>
+          <t>(10)CLEAR BOWL WATER FILTER 1" FPT 50 MESH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BANJO 1-1/2" COUPLER x 1-1/2" FPT THREAD</t>
+          <t>ZF2 CHEMICAL STRAINER W/CHECK VALVE</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barrens &gt; Fittings &amp; Adapters &gt; 201-400</t>
+          <t>Barrens &gt; Fittings &amp; Adapters &gt; 001-200</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BANJO 1-1/2" FPT COUPLING x BARB</t>
+          <t>(100)22mm SCREW COUPLER X 22mm SCREW COUPLER</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PA S.S. SWIVEL 3/8" M/F 5650 PSI</t>
+          <t>BANJO 1-1/2" COUPLER x 1-1/2" FPT THREAD</t>
         </is>
       </c>
     </row>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Barrens &gt; Fittings &amp; Adapters &gt; 401-556</t>
+          <t>Barrens &gt; Fittings &amp; Adapters &gt; 201-400</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PKG OF 10 O-RING BUNA-N FOR 1/4" QC SOCKETS</t>
+          <t>BANJO 1-1/2" FPT COUPLING x BARB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ZGR0750 RS99 2.4 TO 1 GEAR REDUCER FOR 3/4" SHAFTE</t>
+          <t>PA S.S. SWIVEL 3/8" M/F 5650 PSI</t>
         </is>
       </c>
     </row>
@@ -1352,27 +1352,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Barrens &gt; Guns &amp; Wands</t>
+          <t>Barrens &gt; Fittings &amp; Adapters</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Barrens &gt; Guns &amp; Wands</t>
+          <t>Barrens &gt; Fittings &amp; Adapters &gt; 401-556</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>156</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(10)DELUXIFIED MTM 40" ZINC PLATE DUAL LANCE</t>
+          <t>PKG OF 10 O-RING BUNA-N FOR 1/4" QC SOCKETS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ZZDBL72" HEAVY DUTY DUAL LANCE</t>
+          <t>ZGR0750 RS99 2.4 TO 1 GEAR REDUCER FOR 3/4" SHAFTE</t>
         </is>
       </c>
     </row>
@@ -1384,27 +1384,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Barrens &gt; Hose Reels &amp; Parts</t>
+          <t>Barrens &gt; Guns &amp; Wands</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Barrens &gt; Hose Reels &amp; Parts</t>
+          <t>Barrens &gt; Guns &amp; Wands</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(16)A-FRAME HOSE REEL 3/8"x450' 5000PSI</t>
+          <t>(10)DELUXIFIED MTM 40" ZINC PLATE DUAL LANCE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>STACKRACK FOR 150', 300' &amp; 450' SS A-FRAME REELS</t>
+          <t>ZZDBL72" HEAVY DUTY DUAL LANCE</t>
         </is>
       </c>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Barrens &gt; Hoses</t>
+          <t>Barrens &gt; Hose Reels &amp; Parts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Barrens &gt; Hoses &gt; 001-200</t>
+          <t>Barrens &gt; Hose Reels &amp; Parts</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(100)4' CLEAR VINYL HOSE W/DETERGENT FILTER</t>
+          <t>(16)A-FRAME HOSE REEL 3/8"x450' 5000PSI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LIN. FT. BRAID-LOCK BLACK PUSH-ON 1/4" HOSE 300 PS</t>
+          <t>STACKRACK FOR 150', 300' &amp; 450' SS A-FRAME REELS</t>
         </is>
       </c>
     </row>
@@ -1453,22 +1453,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Barrens &gt; Hoses &gt; 201-268</t>
+          <t>Barrens &gt; Hoses &gt; 001-200</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LIN. FT. BRAID-LOCK BLACK PUSH-ON 3/8" HOSE</t>
+          <t>(100)4' CLEAR VINYL HOSE W/DETERGENT FILTER</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WHIRL-A WAY HOSE 62" X 3/8"</t>
+          <t>LIN. FT. BRAID-LOCK BLACK PUSH-ON 1/4" HOSE 300 PS</t>
         </is>
       </c>
     </row>
@@ -1480,27 +1480,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors</t>
+          <t>Barrens &gt; Hoses</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 001-200</t>
+          <t>Barrens &gt; Hoses &gt; 201-268</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>#13 ORIFICE FOR X-JET NOZZLE FOR 3000 TO 4000 PSI</t>
+          <t>LIN. FT. BRAID-LOCK BLACK PUSH-ON 3/8" HOSE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1/4 MEG 4060 WASHJET SPRAY NOZZLE</t>
+          <t>WHIRL-A WAY HOSE 62" X 3/8"</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 201-400</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 001-200</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1/4 MEG 6503 WASHJET SPRAY NOZZLE</t>
+          <t>#13 ORIFICE FOR X-JET NOZZLE FOR 3000 TO 4000 PSI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>90A RED 2.50 GPH HOLLOW CONE NOZZLE</t>
+          <t>1/4 MEG 4060 WASHJET SPRAY NOZZLE</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 401-600</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 201-400</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>90A RED 2.75 GPH HOLLOW CONE NOZZLE</t>
+          <t>1/4 MEG 6503 WASHJET SPRAY NOZZLE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>GP QC 5 NOZZLE KIT 6.5 (0,15,25,40,6540)</t>
+          <t>90A RED 2.50 GPH HOLLOW CONE NOZZLE</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 601-800</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 401-600</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GP QC 5 NOZZLE KIT 7.0 (0,15,25,40,6540)</t>
+          <t>90A RED 2.75 GPH HOLLOW CONE NOZZLE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>REPAIR KIT ROTOJET 4500PSI 4.5</t>
+          <t>GP QC 5 NOZZLE KIT 6.5 (0,15,25,40,6540)</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1613,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 801-937</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 601-800</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>REPAIR KIT ROTOJET 4500PSI 5.0</t>
+          <t>GP QC 5 NOZZLE KIT 7.0 (0,15,25,40,6540)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>X-JET M5 DELUXE VARIABLE NOZZLE #25 KIT 8.5 GPM</t>
+          <t>REPAIR KIT ROTOJET 4500PSI 4.5</t>
         </is>
       </c>
     </row>
@@ -1640,27 +1640,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pressure Washer Systems &amp; Skids</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pressure Washer Systems &amp; Skids</t>
+          <t>Barrens &gt; Nozzles &amp; Injectors &gt; 801-937</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>137</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(10)ST-3600 21 GPM 8700 PSI S.S. SPRAY GUN 1/2" FP</t>
+          <t>REPAIR KIT ROTOJET 4500PSI 5.0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ZMFIL GREEN CAP WATER FILTER 1/2FPT X 1/2MPT</t>
+          <t>X-JET M5 DELUXE VARIABLE NOZZLE #25 KIT 8.5 GPM</t>
         </is>
       </c>
     </row>
@@ -1672,27 +1672,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pump Repair Parts</t>
+          <t>Barrens &gt; Pressure Washer Systems &amp; Skids</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pump Repair Parts &gt; 001-200</t>
+          <t>Barrens &gt; Pressure Washer Systems &amp; Skids</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(2 KITS/PUMP) 33060 VALVE KIT 5CP3120</t>
+          <t>(10)ST-3600 21 GPM 8700 PSI S.S. SPRAY GUN 1/2" FP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>43232 CERAMIC PLUNGER 53,56,57,58,59,60</t>
+          <t>ZMFIL GREEN CAP WATER FILTER 1/2FPT X 1/2MPT</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pump Repair Parts &gt; 201-400</t>
+          <t>Barrens &gt; Pump Repair Parts &gt; 001-200</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>43248 BACK-UP RING, VALVE SEAT (TEFLON)</t>
+          <t>(2 KITS/PUMP) 33060 VALVE KIT 5CP3120</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>98210600 OIL DIP STICK W/O-RING</t>
+          <t>43232 CERAMIC PLUNGER 53,56,57,58,59,60</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pump Repair Parts &gt; 401-600</t>
+          <t>Barrens &gt; Pump Repair Parts &gt; 201-400</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>A1YA-7912 SUNTEC FUEL PUMP</t>
+          <t>43248 BACK-UP RING, VALVE SEAT (TEFLON)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KIT 2542 CERAMIC PISTON 20mmx13mmx45mm</t>
+          <t>98210600 OIL DIP STICK W/O-RING</t>
         </is>
       </c>
     </row>
@@ -1773,22 +1773,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Barrens &gt; Pump Repair Parts &gt; 601-751</t>
+          <t>Barrens &gt; Pump Repair Parts &gt; 401-600</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KIT 2543 CERAMIC PISTONS 22mm XW XWA</t>
+          <t>A1YA-7912 SUNTEC FUEL PUMP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>YUKIT215R REPAIR KIT FOR YU21235 &amp; YU21405 (MFG BE</t>
+          <t>KIT 2542 CERAMIC PISTON 20mmx13mmx45mm</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Barrens &gt; Soft Wash &amp; Foam</t>
+          <t>Barrens &gt; Pump Repair Parts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Barrens &gt; Soft Wash &amp; Foam</t>
+          <t>Barrens &gt; Pump Repair Parts &gt; 601-751</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>151</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>(10)FOAM LANCE ADJ W/LITER BOTTLE</t>
+          <t>KIT 2543 CERAMIC PISTONS 22mm XW XWA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Y5183185 SPACER FOR YLS12T FOAMER</t>
+          <t>YUKIT215R REPAIR KIT FOR YU21235 &amp; YU21405 (MFG BE</t>
         </is>
       </c>
     </row>
@@ -1832,27 +1832,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Barrens &gt; Surface Cleaners &amp; Parts</t>
+          <t>Barrens &gt; Soft Wash &amp; Foam</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Barrens &gt; Surface Cleaners &amp; Parts</t>
+          <t>Barrens &gt; Soft Wash &amp; Foam</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(12)GP 20" FLAT SURFACE CLEANER 8GPM 4000PSI</t>
+          <t>(10)FOAM LANCE ADJ W/LITER BOTTLE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WW3128-4 (26.75") SPRAY BAR 4 TIP BIG GUY 28"</t>
+          <t>Y5183185 SPACER FOR YLS12T FOAMER</t>
         </is>
       </c>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Barrens &gt; Tanks &amp; Chemical Delivery</t>
+          <t>Barrens &gt; Surface Cleaners &amp; Parts</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Barrens &gt; Tanks &amp; Chemical Delivery</t>
+          <t>Barrens &gt; Surface Cleaners &amp; Parts</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(10)FLOAT TANK WITH LID, PLASTIC, 1 GAL.</t>
+          <t>(12)GP 20" FLAT SURFACE CLEANER 8GPM 4000PSI</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>TT9111 3GPM 1500PSI 24MM SOLID SHAFT</t>
+          <t>WW3128-4 (26.75") SPRAY BAR 4 TIP BIG GUY 28"</t>
         </is>
       </c>
     </row>
@@ -1896,364 +1896,364 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Barrens &gt; Unloaders &amp; Flow Control</t>
+          <t>Barrens &gt; Tanks &amp; Chemical Delivery</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Barrens &gt; Unloaders &amp; Flow Control</t>
+          <t>Barrens &gt; Tanks &amp; Chemical Delivery</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(100)EZ-GRIP FGH x 1/2" MPT W/BYPASS FITTING</t>
+          <t>(10)FLOAT TANK WITH LID, PLASTIC, 1 GAL.</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>YKITU5221 KIT REPAIR YU5221 UNLOADER</t>
+          <t>TT9111 3GPM 1500PSI 24MM SOLID SHAFT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EacoChem</t>
+          <t>Barrens</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EacoChem &gt; Fleet Wash Products</t>
+          <t>Barrens &gt; Unloaders &amp; Flow Control</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EacoChem &gt; Fleet Wash Products</t>
+          <t>Barrens &gt; Unloaders &amp; Flow Control</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>140</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AP Plus BC (Purple Plus) - 1 Gallon</t>
+          <t>(100)EZ-GRIP FGH x 1/2" MPT W/BYPASS FITTING</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Truck Wash Supreme SC - 55 Gallon Drum</t>
+          <t>YKITU5221 KIT REPAIR YU5221 UNLOADER</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EacoChem</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EacoChem &gt; New Construction &amp; Restoration</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EacoChem &gt; New Construction &amp; Restoration</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABF Restoration - 1 Gallon</t>
+          <t>Bullseye</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>White Scum Presoak - 55 Gallon Drum</t>
+          <t>White Vinegar</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EacoChem</t>
+          <t>Chemicals &gt; EaCo Chem</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EacoChem &gt; Sealers</t>
+          <t>Chemicals &gt; EaCo Chem</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EacoChem &gt; Sealers</t>
+          <t>Chemicals &gt; EaCo Chem</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EC 101 WB - 1 Gallon</t>
+          <t>Showboat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EC 102 SOL - 55 Gallon Drum</t>
+          <t>Showboat</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EnviroBioCleaner</t>
+          <t>Chemicals &gt; Sweep Away</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EnviroBioCleaner &gt; Multipurpose Cleaner and Degreaser</t>
+          <t>Chemicals &gt; Sweep Away</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EnviroBioCleaner &gt; Multipurpose Cleaner and Degreaser</t>
+          <t>Chemicals &gt; Sweep Away</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EBC Multipurpose Cleaner and Degreaser - 5 Gallon Pail</t>
+          <t>Sweep Away Degreaser 12 Pack</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EBC Multipurpose Cleaner and Degreaser - 55 Gallon Kit</t>
+          <t>Sweep Away Spray Oil Stain Degreaser</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Front9</t>
+          <t>Chemicals &gt; Tagaway/Taginator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Front9 &gt; Concrete Cleaners</t>
+          <t>Chemicals &gt; Tagaway/Taginator</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Front9 &gt; Concrete Cleaners</t>
+          <t>Chemicals &gt; Tagaway/Taginator</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>F9 BARC Rust and Oxidation Remover - 1 Gallon</t>
+          <t>Tagaway 1 gal.</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>F9 Groundskeeper - 5 Gallon Pail</t>
+          <t>Taginator 5 Gal.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>Chemicals &gt; Trident</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INSECO &gt; CONCRETE/STONE/PAVER SEALERS</t>
+          <t>Chemicals &gt; Trident</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INSECO &gt; CONCRETE/STONE/PAVER SEALERS</t>
+          <t>Chemicals &gt; Trident</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1 K URETHANE Five</t>
+          <t>Sea Wall 5 gal.</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SEALTHANE Natural Matte 2 Part Urethane Full Kit</t>
+          <t>Trident Roller Solvent</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>EacoChem</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INSECO &gt; JOINT SAND</t>
+          <t>EacoChem &gt; Fleet Wash Products</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>INSECO &gt; JOINT SAND</t>
+          <t>EacoChem &gt; Fleet Wash Products</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ASH 50# BAG</t>
+          <t>AP Plus BC (Purple Plus) - 1 Gallon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RIVER ROCK 50# BAG</t>
+          <t>Truck Wash Supreme SC - 55 Gallon Drum</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>EacoChem</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INSECO &gt; SEALTHANE Color Packs</t>
+          <t>EacoChem &gt; New Construction &amp; Restoration</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>INSECO &gt; SEALTHANE Color Packs</t>
+          <t>EacoChem &gt; New Construction &amp; Restoration</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Black 128 Ounce</t>
+          <t>ABF Restoration - 1 Gallon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Yellow Oxide 4 Ounce</t>
+          <t>White Scum Presoak - 55 Gallon Drum</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>EacoChem</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INSECO &gt; SOLVENT CONCRETE STAIN/SEALERS</t>
+          <t>EacoChem &gt; Sealers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>INSECO &gt; SOLVENT CONCRETE STAIN/SEALERS</t>
+          <t>EacoChem &gt; Sealers</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Accent Base Five</t>
+          <t>EC 101 WB - 1 Gallon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>White Base Gallon</t>
+          <t>EC 102 SOL - 55 Gallon Drum</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>EnviroBioCleaner</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>INSECO &gt; SPECIALTY FINISHES</t>
+          <t>EnviroBioCleaner &gt; Multipurpose Cleaner and Degreaser</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>INSECO &gt; SPECIALTY FINISHES</t>
+          <t>EnviroBioCleaner &gt; Multipurpose Cleaner and Degreaser</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>100% Acrylic HOT STUCCO Primer 1 Gallon</t>
+          <t>EBC Multipurpose Cleaner and Degreaser - 5 Gallon Pail</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TEX RX ANTI SKID ADDITIVE 6 OZ</t>
+          <t>EBC Multipurpose Cleaner and Degreaser - 55 Gallon Kit</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>INSECO &gt; STRIPPERS &amp; CLEANERS</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INSECO &gt; STRIPPERS &amp; CLEANERS</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2263,332 +2263,332 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NPS Rx Natural Paint Stripper Gel Five</t>
+          <t>8012PRO-35HG</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>PSR Paver Sealer Remover Spray Gallon</t>
+          <t>Whisper Wash Mini Mondo 31"</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>Front9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>INSECO &gt; WOOD Rx Color Packs</t>
+          <t>Front9 &gt; Concrete Cleaners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>INSECO &gt; WOOD Rx Color Packs</t>
+          <t>Front9 &gt; Concrete Cleaners</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Color Pack Cedar Five</t>
+          <t>F9 BARC Rust and Oxidation Remover - 1 Gallon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Color Pack Weatherd Gray Gallon</t>
+          <t>F9 Groundskeeper - 5 Gallon Pail</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INSECO</t>
+          <t>H &amp; G</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INSECO &gt; WOOD SEALERS</t>
+          <t>H &amp; G &gt; Chemicals &gt; Sweep Away</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INSECO &gt; WOOD SEALERS</t>
+          <t>H &amp; G &gt; Chemicals &gt; Sweep Away</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DECK Rx Accent Five</t>
+          <t>Sweep Away Combo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>WOOD Rx ultra Weathered Gray Gallon</t>
+          <t>Sweep Away Combo</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Accessories</t>
+          <t>INSECO &gt; CONCRETE/STONE/PAVER SEALERS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Accessories</t>
+          <t>INSECO &gt; CONCRETE/STONE/PAVER SEALERS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bulb Changer Kit</t>
+          <t>1 K URETHANE Five</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bulb Changer Kit with Pole</t>
+          <t>SEALTHANE Natural Matte 2 Part Urethane Full Kit</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Auto Cleaning</t>
+          <t>INSECO &gt; JOINT SAND</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Auto Cleaning</t>
+          <t>INSECO &gt; JOINT SAND</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Acrylic Squeegee</t>
+          <t>ASH 50# BAG</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wrap around Flo Brush</t>
+          <t>RIVER ROCK 50# BAG</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Backflip</t>
+          <t>INSECO &gt; SEALTHANE Color Packs</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Backflip</t>
+          <t>INSECO &gt; SEALTHANE Color Packs</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BackFlip Handle Brass</t>
+          <t>Black 128 Ounce</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BackFlip, Stainless Steel, 18"</t>
+          <t>Yellow Oxide 4 Ounce</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Brushes &amp; Accessories</t>
+          <t>INSECO &gt; SOLVENT CONCRETE STAIN/SEALERS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Brushes &amp; Accessories</t>
+          <t>INSECO &gt; SOLVENT CONCRETE STAIN/SEALERS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cleaning Clamp</t>
+          <t>Accent Base Five</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Toilet Bowl Brush</t>
+          <t>White Base Gallon</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Buckets</t>
+          <t>INSECO &gt; SPECIALTY FINISHES</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Buckets</t>
+          <t>INSECO &gt; SPECIALTY FINISHES</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3 1/2 Gallon Bucket</t>
+          <t>100% Acrylic HOT STUCCO Primer 1 Gallon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Super Bucket, Snap-On Lid</t>
+          <t>TEX RX ANTI SKID ADDITIVE 6 OZ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Channels</t>
+          <t>INSECO &gt; STRIPPERS &amp; CLEANERS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Channels</t>
+          <t>INSECO &gt; STRIPPERS &amp; CLEANERS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aluminum Channel with Rubber 12"</t>
+          <t>NPS Rx Natural Paint Stripper Gel Five</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Super Channel 36"</t>
+          <t>PSR Paver Sealer Remover Spray Gallon</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Clean Up Tools</t>
+          <t>INSECO &gt; WOOD Rx Color Packs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Clean Up Tools</t>
+          <t>INSECO &gt; WOOD Rx Color Packs</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grip'n Grab 16"</t>
+          <t>Color Pack Cedar Five</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Trash Picker Replacement Tip</t>
+          <t>Color Pack Weatherd Gray Gallon</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JRacenstein</t>
+          <t>INSECO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Complete Squeegees</t>
+          <t>INSECO &gt; WOOD SEALERS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Complete Squeegees</t>
+          <t>INSECO &gt; WOOD SEALERS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>All-Purpose Squeegee 10"</t>
+          <t>DECK Rx Accent Five</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shower Sweep White</t>
+          <t>WOOD Rx ultra Weathered Gray Gallon</t>
         </is>
       </c>
     </row>
@@ -2600,27 +2600,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Dusters</t>
+          <t>JRacenstein &gt; Accessories</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Dusters</t>
+          <t>JRacenstein &gt; Accessories</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ceiling Fan Brush</t>
+          <t>Bulb Changer Kit</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Turkey Feather Duster, 14"</t>
+          <t>Bulb Changer Kit with Pole</t>
         </is>
       </c>
     </row>
@@ -2632,27 +2632,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Floor Squeegee Rubber</t>
+          <t>JRacenstein &gt; Auto Cleaning</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Floor Squeegee Rubber</t>
+          <t>JRacenstein &gt; Auto Cleaning</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Black Replacement Rubber for Straight and Curved Aluminun Floor Squeeges 18"</t>
+          <t>Acrylic Squeegee</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Replacement Rubber for Industrial Steel Floor Squeegees 36"</t>
+          <t>Wrap around Flo Brush</t>
         </is>
       </c>
     </row>
@@ -2664,27 +2664,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Floor Squeegees</t>
+          <t>JRacenstein &gt; Backflip</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Floor Squeegees</t>
+          <t>JRacenstein &gt; Backflip</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>30" Curved Aluminum Floor Squeegee</t>
+          <t>BackFlip Handle Brass</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wooden Floor Squeegee Handles 60"</t>
+          <t>BackFlip, Stainless Steel, 18"</t>
         </is>
       </c>
     </row>
@@ -2696,27 +2696,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Holsters</t>
+          <t>JRacenstein &gt; Brushes &amp; Accessories</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Holsters</t>
+          <t>JRacenstein &gt; Brushes &amp; Accessories</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Double Loop Nylon Holster</t>
+          <t>Cleaning Clamp</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utility Pouch</t>
+          <t>Toilet Bowl Brush</t>
         </is>
       </c>
     </row>
@@ -2728,27 +2728,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Kits</t>
+          <t>JRacenstein &gt; Buckets</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Kits</t>
+          <t>JRacenstein &gt; Buckets</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>All-Purpose Window Cleaning Kit</t>
+          <t>3 1/2 Gallon Bucket</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Window Cleaning Kit with Case</t>
+          <t>Super Bucket, Snap-On Lid</t>
         </is>
       </c>
     </row>
@@ -2760,27 +2760,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Microfiber Cloths</t>
+          <t>JRacenstein &gt; Channels</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Microfiber Cloths</t>
+          <t>JRacenstein &gt; Channels</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>All Purpose MicroSwipe 13 x 13</t>
+          <t>Aluminum Channel with Rubber 12"</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wood &amp; Furniture Microfiber Cloths 13" X 13"</t>
+          <t>Super Channel 36"</t>
         </is>
       </c>
     </row>
@@ -2792,27 +2792,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Point of Purchase Displays</t>
+          <t>JRacenstein &gt; Clean Up Tools</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Point of Purchase Displays</t>
+          <t>JRacenstein &gt; Clean Up Tools</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Complete Cleaning Display</t>
+          <t>Grip'n Grab 16"</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Window Cleaning Refill Kit</t>
+          <t>Trash Picker Replacement Tip</t>
         </is>
       </c>
     </row>
@@ -2824,27 +2824,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Pole Custom Packs</t>
+          <t>JRacenstein &gt; Complete Squeegees</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Pole Custom Packs</t>
+          <t>JRacenstein &gt; Complete Squeegees</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Various Poles Custom Packs</t>
+          <t>All-Purpose Squeegee 10"</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Various Poles Custom Packs</t>
+          <t>Shower Sweep White</t>
         </is>
       </c>
     </row>
@@ -2856,27 +2856,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Poles &amp; Pole Accessories</t>
+          <t>JRacenstein &gt; Dusters</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Poles &amp; Pole Accessories</t>
+          <t>JRacenstein &gt; Dusters</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Angle Adapter</t>
+          <t>Ceiling Fan Brush</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Replacement Grips 4-Sec</t>
+          <t>Turkey Feather Duster, 14"</t>
         </is>
       </c>
     </row>
@@ -2888,27 +2888,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Rubber</t>
+          <t>JRacenstein &gt; Floor Squeegee Rubber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Rubber</t>
+          <t>JRacenstein &gt; Floor Squeegee Rubber</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>End Clips</t>
+          <t>Black Replacement Rubber for Straight and Curved Aluminun Floor Squeeges 18"</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>T-Shaped Rubber, 36"</t>
+          <t>Replacement Rubber for Industrial Steel Floor Squeegees 36"</t>
         </is>
       </c>
     </row>
@@ -2920,27 +2920,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Scrapers &amp; Floor Scrapers</t>
+          <t>JRacenstein &gt; Floor Squeegees</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Scrapers &amp; Floor Scrapers</t>
+          <t>JRacenstein &gt; Floor Squeegees</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ettore Champion Blade Holder 5"</t>
+          <t>30" Curved Aluminum Floor Squeegee</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Scrapemaster Replacement Blades 4"</t>
+          <t>Wooden Floor Squeegee Handles 60"</t>
         </is>
       </c>
     </row>
@@ -2952,27 +2952,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Sleeves</t>
+          <t>JRacenstein &gt; Holsters</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Sleeves</t>
+          <t>JRacenstein &gt; Holsters</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Advanced Microfiber, Sleeve, 10"</t>
+          <t>Double Loop Nylon Holster</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Porcupine Scrubber, Sleeve, 22"</t>
+          <t>Utility Pouch</t>
         </is>
       </c>
     </row>
@@ -2984,27 +2984,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Soap</t>
+          <t>JRacenstein &gt; Kits</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Soap</t>
+          <t>JRacenstein &gt; Kits</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>1 Gal Squeegee Off</t>
+          <t>All-Purpose Window Cleaning Kit</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Squeege-Off Liquid Soap, Concentrate 32oz</t>
+          <t>Window Cleaning Kit with Case</t>
         </is>
       </c>
     </row>
@@ -3016,27 +3016,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Squeegee Handles</t>
+          <t>JRacenstein &gt; Microfiber Cloths</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; Squeegee Handles</t>
+          <t>JRacenstein &gt; Microfiber Cloths</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aluminum Handle</t>
+          <t>All Purpose MicroSwipe 13 x 13</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zero Degree Handle</t>
+          <t>Wood &amp; Furniture Microfiber Cloths 13" X 13"</t>
         </is>
       </c>
     </row>
@@ -3048,283 +3048,283 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; T-Bars</t>
+          <t>JRacenstein &gt; Point of Purchase Displays</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>JRacenstein &gt; T-Bars</t>
+          <t>JRacenstein &gt; Point of Purchase Displays</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pro + T-Bar 10"</t>
+          <t>Complete Cleaning Display</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Taper T-Bar T-Bar, 18"</t>
+          <t>Window Cleaning Refill Kit</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Accessories &amp; Misc</t>
+          <t>JRacenstein &gt; Pole Custom Packs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Accessories &amp; Misc</t>
+          <t>JRacenstein &gt; Pole Custom Packs</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>.975 Brass Ferrule for Fluid</t>
+          <t>Various Poles Custom Packs</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Xforce Stainless Steel Performance 4 tip bar Mondo</t>
+          <t>Various Poles Custom Packs</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Chemicals &amp; Sealers</t>
+          <t>JRacenstein &gt; Poles &amp; Pole Accessories</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Chemicals &amp; Sealers</t>
+          <t>JRacenstein &gt; Poles &amp; Pole Accessories</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>16oz Window Mauler</t>
+          <t>Angle Adapter</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Window Mauler Gallon</t>
+          <t>Replacement Grips 4-Sec</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Complete Pumps</t>
+          <t>JRacenstein &gt; Rubber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Complete Pumps</t>
+          <t>JRacenstein &gt; Rubber</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2200 PSI 2.2 GPM 7/8" Vertical Shaft</t>
+          <t>End Clips</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VRT-3 Unloader w/built-in EZ start 8.0gpm 4500PSI MAX</t>
+          <t>T-Shaped Rubber, 36"</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Drive Components &amp; Hardware</t>
+          <t>JRacenstein &gt; Scrapers &amp; Floor Scrapers</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Drive Components &amp; Hardware</t>
+          <t>JRacenstein &gt; Scrapers &amp; Floor Scrapers</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>#6 300 SERIES 5/16=7/8 INNER DIAMETER Mini Clamp</t>
+          <t>Ettore Champion Blade Holder 5"</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ULTRACLEAN 19"HC Handle</t>
+          <t>Scrapemaster Replacement Blades 4"</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Electrical &amp; Burner Controls</t>
+          <t>JRacenstein &gt; Sleeves</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Electrical &amp; Burner Controls</t>
+          <t>JRacenstein &gt; Sleeves</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(Rectifier) 20A</t>
+          <t>Advanced Microfiber, Sleeve, 10"</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Switch; Oil Level</t>
+          <t>Porcupine Scrubber, Sleeve, 22"</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Engines &amp; Engine Parts</t>
+          <t>JRacenstein &gt; Soap</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Engines &amp; Engine Parts &gt; 001-200</t>
+          <t>JRacenstein &gt; Soap</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>12v rocker switch Carling 10C587 V1D1</t>
+          <t>1 Gal Squeegee Off</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Throttle Control Assy GX140-160-200, 168F-196F</t>
+          <t>Squeege-Off Liquid Soap, Concentrate 32oz</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Engines &amp; Engine Parts</t>
+          <t>JRacenstein &gt; Squeegee Handles</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Engines &amp; Engine Parts &gt; 201-208</t>
+          <t>JRacenstein &gt; Squeegee Handles</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Throttle Control Assy GX240-270 173F-177F</t>
+          <t>Aluminum Handle</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>YGR1125P31 B31 1-1/8" engine shaft General Pumps All</t>
+          <t>Zero Degree Handle</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MPWSR</t>
+          <t>JRacenstein</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Filters &amp; Strainers</t>
+          <t>JRacenstein &gt; T-Bars</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Filters &amp; Strainers</t>
+          <t>JRacenstein &gt; T-Bars</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>1 1/2" Poly Y Strainer 80 Mesh</t>
+          <t>Pro + T-Bar 10"</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Y15373400 PA gearbox oil sight glass</t>
+          <t>Taper T-Bar T-Bar, 18"</t>
         </is>
       </c>
     </row>
@@ -3336,27 +3336,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Fittings &amp; Adapters</t>
+          <t>MPWSR &gt; Accessories &amp; Misc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Fittings &amp; Adapters &gt; 001-200</t>
+          <t>MPWSR &gt; Accessories &amp; Misc</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>1 1/2 x 1 1/4 Fernco</t>
+          <t>.975 Brass Ferrule for Fluid</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Plug 3/8" G AR3120690 (AR45 #50 / AR60 #74)</t>
+          <t>Xforce Stainless Steel Performance 4 tip bar Mondo</t>
         </is>
       </c>
     </row>
@@ -3368,27 +3368,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Fittings &amp; Adapters</t>
+          <t>MPWSR &gt; Chemicals &amp; Sealers</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Fittings &amp; Adapters &gt; 201-228</t>
+          <t>MPWSR &gt; Chemicals &amp; Sealers</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Poly Elbow 1/2" mpt x 1/4" barb</t>
+          <t>16oz Window Mauler</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>TSF2221 8.5-10.2GPM @ 3000PSI 1450/1750</t>
+          <t>Window Mauler Gallon</t>
         </is>
       </c>
     </row>
@@ -3400,27 +3400,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Guns &amp; Wands</t>
+          <t>MPWSR &gt; Complete Pumps</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Guns &amp; Wands</t>
+          <t>MPWSR &gt; Complete Pumps</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1 ft Aluminum Extension Wand Assembly With Quick Connects</t>
+          <t>2200 PSI 2.2 GPM 7/8" Vertical Shaft</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Universal Spot spray gun</t>
+          <t>VRT-3 Unloader w/built-in EZ start 8.0gpm 4500PSI MAX</t>
         </is>
       </c>
     </row>
@@ -3432,27 +3432,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Hose Reels &amp; Parts</t>
+          <t>MPWSR &gt; Drive Components &amp; Hardware</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Hose Reels &amp; Parts</t>
+          <t>MPWSR &gt; Drive Components &amp; Hardware</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>1/2 304 STAINLESS STEEL ELBOW Titan reel</t>
+          <t>#6 300 SERIES 5/16=7/8 INNER DIAMETER Mini Clamp</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Titan Reel Side Panel</t>
+          <t>ULTRACLEAN 19"HC Handle</t>
         </is>
       </c>
     </row>
@@ -3464,27 +3464,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Hoses</t>
+          <t>MPWSR &gt; Electrical &amp; Burner Controls</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Hoses</t>
+          <t>MPWSR &gt; Electrical &amp; Burner Controls</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1 1/2" Clear Poly Braided Hose (per ft)</t>
+          <t>(Rectifier) 20A</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Whip line 8' 4000 psi black hose 3/8</t>
+          <t>Switch; Oil Level</t>
         </is>
       </c>
     </row>
@@ -3496,27 +3496,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Nozzles &amp; Injectors</t>
+          <t>MPWSR &gt; Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Nozzles &amp; Injectors</t>
+          <t>MPWSR &gt; Engines &amp; Engine Parts &gt; 001-200</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1.8mm Chemical Injector (100774) w/ SS QC's</t>
+          <t>12v rocker switch Carling 10C587 V1D1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>White Nozzle 40 Degree Tip - 12 GPM</t>
+          <t>Throttle Control Assy GX140-160-200, 168F-196F</t>
         </is>
       </c>
     </row>
@@ -3528,27 +3528,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids</t>
+          <t>MPWSR &gt; Engines &amp; Engine Parts</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids &gt; 001-200</t>
+          <t>MPWSR &gt; Engines &amp; Engine Parts &gt; 201-208</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>1" Banjo T Strainer 80 Mesh</t>
+          <t>Throttle Control Assy GX240-270 173F-177F</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Manatee Gear Drive 5.5GPM @ 3500PSI w/ GX630 &amp; Comet RW5535 Pump</t>
+          <t>YGR1125P31 B31 1-1/8" engine shaft General Pumps All</t>
         </is>
       </c>
     </row>
@@ -3560,27 +3560,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids</t>
+          <t>MPWSR &gt; Filters &amp; Strainers</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids &gt; 201-361</t>
+          <t>MPWSR &gt; Filters &amp; Strainers</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Manatee Gear Drive 5.5GPM @ 3500PSI w/ GX630 &amp; Comet RW5535 Pump (K7 Unloader)</t>
+          <t>1 1/2" Poly Y Strainer 80 Mesh</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ZWD-K/AXD/BXD Unloader kit</t>
+          <t>Y15373400 PA gearbox oil sight glass</t>
         </is>
       </c>
     </row>
@@ -3592,27 +3592,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pump Repair Parts</t>
+          <t>MPWSR &gt; Fittings &amp; Adapters</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Pump Repair Parts</t>
+          <t>MPWSR &gt; Fittings &amp; Adapters &gt; 001-200</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0501.0168.00 DELIVERY MANIFOLD COMPLETE P36/10</t>
+          <t>1 1/2 x 1 1/4 Fernco</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ZWD-K Valve Kit</t>
+          <t>Poly Elbow 1/2" mpt x 1/4" barb</t>
         </is>
       </c>
     </row>
@@ -3624,27 +3624,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Skids</t>
+          <t>MPWSR &gt; Fittings &amp; Adapters</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Skids</t>
+          <t>MPWSR &gt; Fittings &amp; Adapters &gt; 201-227</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Truck Mount Skid CRX680</t>
+          <t>PUMP KIT 171 COMPLETE SEAL PACKING KIT (20MM) With Brass</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Truck Mount Skid CRX680</t>
+          <t>TSF2221 8.5-10.2GPM @ 3000PSI 1450/1750</t>
         </is>
       </c>
     </row>
@@ -3656,27 +3656,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Soft Wash &amp; Foam</t>
+          <t>MPWSR &gt; Guns &amp; Wands</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Soft Wash &amp; Foam &gt; 001-200</t>
+          <t>MPWSR &gt; Guns &amp; Wands</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>86</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>1" Metering Valve</t>
+          <t>1 ft Aluminum Extension Wand Assembly With Quick Connects</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rampage 1/2" Red 300' softwash hose with STAINLESS STEEL crimped ends</t>
+          <t>Universal Spot spray gun</t>
         </is>
       </c>
     </row>
@@ -3688,27 +3688,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Soft Wash &amp; Foam</t>
+          <t>MPWSR &gt; Hose Reels &amp; Parts</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Soft Wash &amp; Foam &gt; 201-250</t>
+          <t>MPWSR &gt; Hose Reels &amp; Parts</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rampage 1/2" Yellow 200' softwash hose NO CRIMPS</t>
+          <t>1/2 304 STAINLESS STEEL ELBOW Titan reel</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Xjet M5 Twist Nozzle - 7-12 GPM</t>
+          <t>Titan Reel Side Panel</t>
         </is>
       </c>
     </row>
@@ -3720,27 +3720,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Surface Cleaners &amp; Parts</t>
+          <t>MPWSR &gt; Hoses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Surface Cleaners &amp; Parts &gt; 001-200</t>
+          <t>MPWSR &gt; Hoses</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>131</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>001/4 Meg SurfaceCleaner Nozzle 6.5 GPM 0 Degree 00065</t>
+          <t>1 1/2" Clear Poly Braided Hose (per ft)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Roto EZE Surface Cleaner Replacement Cover</t>
+          <t>Whip line 8' 4000 psi black hose 3/8</t>
         </is>
       </c>
     </row>
@@ -3752,27 +3752,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Surface Cleaners &amp; Parts</t>
+          <t>MPWSR &gt; Nozzles &amp; Injectors</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Surface Cleaners &amp; Parts &gt; 201-251</t>
+          <t>MPWSR &gt; Nozzles &amp; Injectors</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>158</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Solid handle for surface cleaners</t>
+          <t>1.8mm Chemical Injector (100774) w/ SS QC's</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Xforce Stainless Steel Performance 4 tip bar Ultra Clean 19 Classic 19</t>
+          <t>White Nozzle 40 Degree Tip - 12 GPM</t>
         </is>
       </c>
     </row>
@@ -3784,27 +3784,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Tanks &amp; Chemical Delivery</t>
+          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Tanks &amp; Chemical Delivery</t>
+          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids &gt; 001-200</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>1 1/2" Bulkhead</t>
+          <t>1" Banjo T Strainer 80 Mesh</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>ZWD 5030 direct drive bare pump 6305.2400.00</t>
+          <t>Manatee Gear Drive 5.5GPM @ 3500PSI w/ GX630 &amp; Comet RW5535 Pump</t>
         </is>
       </c>
     </row>
@@ -3816,315 +3816,923 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Unloaders &amp; Flow Control</t>
+          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MPWSR &gt; Unloaders &amp; Flow Control</t>
+          <t>MPWSR &gt; Pressure Washer Systems &amp; Skids &gt; 201-361</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>**SPECIAL FOR PSI ONLY** PMR RW 5535S-VRT3-310EZ W/BYPASS &amp; THERM RELIEF</t>
+          <t>Manatee Gear Drive 5.5GPM @ 3500PSI w/ GX630 &amp; Comet RW5535 Pump (K7 Unloader)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>VRT-3 Repair Kit</t>
+          <t>ZWD-K/AXD/BXD Unloader kit</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RCCT</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RCCT &gt; Trailers</t>
+          <t>MPWSR &gt; Pump Repair Parts</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RCCT &gt; Trailers</t>
+          <t>MPWSR &gt; Pump Repair Parts</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>178</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>77 x 10 Tandem Axle Utility Trailer - No Ramp</t>
+          <t>0501.0168.00 DELIVERY MANIFOLD COMPLETE P36/10</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>77 x 10 Tandem Axle Utility Trailer - No Ramp</t>
+          <t>ZWD-K Valve Kit</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Trident</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Trident &gt; 2 Part Sealers</t>
+          <t>MPWSR &gt; Skids</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Trident &gt; 2 Part Sealers</t>
+          <t>MPWSR &gt; Skids</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hurricane Cat 4 Full Kit</t>
+          <t>Truck Mount Skid CRX680</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hurricane Cat 5 Half Kit</t>
+          <t>Truck Mount Skid CRX680</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Trident</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Trident &gt; Cleaners</t>
+          <t>MPWSR &gt; Soft Wash &amp; Foam</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Trident &gt; Cleaners</t>
+          <t>MPWSR &gt; Soft Wash &amp; Foam &gt; 001-200</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Point Break - 4 Gallon Case (per gallon)</t>
+          <t>1" Metering Valve</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Wipe Out - 5 Gallon Pail</t>
+          <t>Rampage 1/2" Red 300' softwash hose with crimped ends</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Trident</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Trident &gt; Sand</t>
+          <t>MPWSR &gt; Soft Wash &amp; Foam</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Trident &gt; Sand</t>
+          <t>MPWSR &gt; Soft Wash &amp; Foam &gt; 201-251</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Joint Sand - Black - 50 lb bag</t>
+          <t>Rampage 1/2" Red 300' softwash hose with STAINLESS STEEL crimped ends</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Polysweep - Tan - 50 lb bag</t>
+          <t>Xjet M5 Twist Nozzle - 7-12 GPM</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Trident</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Trident &gt; Sealers</t>
+          <t>MPWSR &gt; Surface Cleaners &amp; Parts</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Trident &gt; Sealers</t>
+          <t>MPWSR &gt; Surface Cleaners &amp; Parts &gt; 001-200</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>200</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Break Wall - 5 Gallon Pail</t>
+          <t>001/4 Meg SurfaceCleaner Nozzle 6.5 GPM 0 Degree 00065</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Typhoon - 5 Gallon Pail</t>
+          <t>Roto EZE Surface Cleaner Replacement Cover</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tucker &gt; Accessories</t>
+          <t>MPWSR &gt; Surface Cleaners &amp; Parts</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tucker &gt; Accessories</t>
+          <t>MPWSR &gt; Surface Cleaners &amp; Parts &gt; 201-251</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>0-160 psi Pressure Gauge Liquid Filled</t>
+          <t>Solid handle for surface cleaners</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>XL Nylon Alpha Brush</t>
+          <t>Xforce Stainless Steel Performance 4 tip bar Ultra Clean 19 Classic 19</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tucker &gt; Catalog</t>
+          <t>MPWSR &gt; Tanks &amp; Chemical Delivery</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Tucker &gt; Catalog</t>
+          <t>MPWSR &gt; Tanks &amp; Chemical Delivery</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>1/2 Black Tubing (per 10 foot length)</t>
+          <t>1 1/2" Bulkhead</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wood Cone Tip for Acme Tips</t>
+          <t>ZWD 5030 direct drive bare pump 6305.2400.00</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tucker</t>
+          <t>MPWSR</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tucker &gt; Pure Water Systems</t>
+          <t>MPWSR &gt; Unloaders &amp; Flow Control</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Tucker &gt; Pure Water Systems</t>
+          <t>MPWSR &gt; Unloaders &amp; Flow Control</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>1 cubic foot of Tucker DI resin in Bucket</t>
+          <t>**SPECIAL FOR PSI ONLY** PMR RW 5535S-VRT3-310EZ W/BYPASS &amp; THERM RELIEF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Water-Fed Delivery Pump</t>
+          <t>VRT-3 Repair Kit</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>Manatee</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Manatee</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Manatee</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1/2 hose x 1/2 M Pipe Swivel Crimp</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Xforce SS 4 tip bar Ground Force Spray Bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Maxim Mart</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Maxim Mart &gt; Window Cleaning</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Maxim Mart &gt; Window Cleaning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Blue Microfiber Glass Cloth / Towel</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Microfiber Waffle Weave Towel</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Parts</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1/4" MPT Nozzle 25 Degree 60 gpm</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>VAM03</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>RCCT</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>RCCT &gt; Trailers</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>RCCT &gt; Trailers</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>77 x 10 Tandem Axle Utility Trailer - No Ramp</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>77 x 10 Tandem Axle Utility Trailer - No Ramp</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Sand &gt; Chemicals &gt; Trident</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Sand &gt; Chemicals &gt; Trident</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Joint Sand BLACK</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>PolySweep TAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Sealer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Sealer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Sealer</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>EC 101 WB 1 Gal.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Micro-Seal - 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Pressure Washing Equipment Maintenance / PM</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pressure Washing Equipment Maintenance / PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>14" Unger Microfiber Window Combi</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Yellow Microfiber Towel</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Tools</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tools &gt; Chemicals &gt; Tagaway/Taginator</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Tools &gt; Chemicals &gt; Tagaway/Taginator</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Tagsprayer</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Tagsprayer</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Trident &gt; 2 Part Sealers</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Trident &gt; 2 Part Sealers</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Hurricane Cat 4 Full Kit</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Hurricane Cat 5 Half Kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Trident &gt; Cleaners</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Trident &gt; Cleaners</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Point Break - 4 Gallon Case (per gallon)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Wipe Out - 5 Gallon Pail</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Trident &gt; Sand</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Trident &gt; Sand</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Joint Sand - Black - 50 lb bag</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Polysweep - Tan - 50 lb bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Trident</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Trident &gt; Sealers</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Trident &gt; Sealers</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Break Wall - 5 Gallon Pail</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Typhoon - 5 Gallon Pail</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>Tucker</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Accessories</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Accessories</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0-160 psi Pressure Gauge Liquid Filled</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>XL Nylon Alpha Brush</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Catalog</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Catalog</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1/2 Black Tubing (per 10 foot length)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Wood Cone Tip for Acme Tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Pure Water Systems</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Tucker &gt; Pure Water Systems</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1 cubic foot of Tucker DI resin in Bucket</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Water-Fed Delivery Pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Tucker</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
         <is>
           <t>Tucker &gt; Water Fed Pole Parts</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Tucker &gt; Water Fed Pole Parts</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>#1 Section for 50HMw/ clamp</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>V2 Lever Complete for CF Pole Clamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Uncategorized</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1/2 10 pack o ring</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Wooster R054 2 -4 Extension Pole</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Window Cleaning</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Window Cleaning</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Window Cleaning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>3M 08003 Pad,White,10"L</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Unger Ninja Scraper 6 Inch</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Window Cleaning &gt; Sorbo</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Window Cleaning &gt; Sorbo</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Window Cleaning &gt; Sorbo</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Sorbo 14" Fixed T-Bar</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Sorbo Yellow Jacket Sleeve with Brass Snaps 18in</t>
         </is>
       </c>
     </row>
